--- a/CO国試data/CO_questions_2019.xlsx
+++ b/CO国試data/CO_questions_2019.xlsx
@@ -542,15 +542,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -599,7 +599,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>False</t>
@@ -635,15 +634,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>遺伝</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -692,7 +691,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>False</t>
@@ -728,15 +726,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>免疫機構</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -785,7 +783,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>False</t>
@@ -824,12 +821,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>病態の基礎</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -878,7 +875,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>True</t>
@@ -917,12 +913,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>疾患の診断と治療</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -971,7 +967,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>False</t>
@@ -1007,15 +1002,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1064,7 +1059,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>False</t>
@@ -1100,15 +1094,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1157,7 +1151,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>False</t>
@@ -1193,15 +1186,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>3</v>
       </c>
@@ -1250,7 +1243,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>False</t>
@@ -1286,15 +1278,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>心身の成長・発達、加齢</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1343,7 +1335,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>False</t>
@@ -1379,15 +1370,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -1436,7 +1427,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>True</t>
@@ -1472,15 +1462,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>3</v>
       </c>
@@ -1529,7 +1519,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>False</t>
@@ -1565,15 +1554,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>3</v>
       </c>
@@ -1622,7 +1611,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1658,15 +1646,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -1715,7 +1703,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1751,15 +1738,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>3</v>
       </c>
@@ -1808,7 +1795,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>True</t>
@@ -1844,15 +1830,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -1901,7 +1887,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>False</t>
@@ -1937,15 +1922,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -1994,7 +1979,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>False</t>
@@ -2030,15 +2014,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -2087,7 +2071,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>False</t>
@@ -2123,15 +2106,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>3</v>
       </c>
@@ -2180,7 +2163,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>False</t>
@@ -2216,15 +2198,15 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -2273,7 +2255,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>False</t>
@@ -2309,15 +2290,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -2366,7 +2347,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>False</t>
@@ -2402,15 +2382,15 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>3</v>
       </c>
@@ -2459,7 +2439,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>False</t>
@@ -2495,15 +2474,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>4</v>
       </c>
@@ -2593,15 +2572,15 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>3</v>
       </c>
@@ -2650,7 +2629,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>False</t>
@@ -2686,15 +2664,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>3</v>
       </c>
@@ -2743,7 +2721,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>True</t>
@@ -2782,12 +2759,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>1</v>
       </c>
@@ -2836,7 +2813,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>False</t>
@@ -2872,15 +2848,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -2929,7 +2905,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>False</t>
@@ -2965,15 +2940,15 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -3022,7 +2997,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>False</t>
@@ -3058,15 +3032,15 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -3115,7 +3089,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>False</t>
@@ -3151,15 +3124,15 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>3</v>
       </c>
@@ -3208,7 +3181,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>False</t>
@@ -3244,15 +3216,15 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>3</v>
       </c>
@@ -3301,7 +3273,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>False</t>
@@ -3337,15 +3308,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>3</v>
       </c>
@@ -3394,7 +3365,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>False</t>
@@ -3430,15 +3400,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>3</v>
       </c>
@@ -3487,7 +3457,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>True</t>
@@ -3523,15 +3492,15 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -3580,7 +3549,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>False</t>
@@ -3616,15 +3584,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>4</v>
       </c>
@@ -3714,15 +3682,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>3</v>
       </c>
@@ -3812,15 +3780,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>2</v>
       </c>
@@ -3869,7 +3837,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>False</t>
@@ -3905,15 +3872,15 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>1</v>
       </c>
@@ -3962,7 +3929,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>False</t>
@@ -3998,15 +3964,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4055,7 +4021,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>False</t>
@@ -4091,15 +4056,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>2</v>
       </c>
@@ -4148,7 +4113,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>False</t>
@@ -4184,15 +4148,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -4241,7 +4205,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>False</t>
@@ -4277,15 +4240,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>1</v>
       </c>
@@ -4334,7 +4297,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>False</t>
@@ -4370,15 +4332,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>3</v>
       </c>
@@ -4427,7 +4389,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>True</t>
@@ -4463,15 +4424,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>3</v>
       </c>
@@ -4520,7 +4481,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>True</t>
@@ -4556,15 +4516,15 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -4613,7 +4573,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
           <t>False</t>
@@ -4649,15 +4608,15 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>3</v>
       </c>
@@ -4706,7 +4665,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
           <t>False</t>
@@ -4742,15 +4700,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>3</v>
       </c>
@@ -4799,7 +4757,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>False</t>
@@ -4835,15 +4792,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>2</v>
       </c>
@@ -4892,7 +4849,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
           <t>False</t>
@@ -4928,15 +4884,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>3</v>
       </c>
@@ -4985,7 +4941,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>True</t>
@@ -5021,15 +4976,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>3</v>
       </c>
@@ -5078,7 +5033,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>True</t>
@@ -5114,15 +5068,15 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>3</v>
       </c>
@@ -5171,7 +5125,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>False</t>
@@ -5207,15 +5160,15 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>3</v>
       </c>
@@ -5264,7 +5217,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>False</t>
@@ -5300,15 +5252,15 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>4</v>
       </c>
@@ -5357,7 +5309,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
           <t>True</t>
@@ -5393,15 +5344,15 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>2</v>
       </c>
@@ -5450,7 +5401,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>True</t>
@@ -5486,15 +5436,15 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>2</v>
       </c>
@@ -5543,7 +5493,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>False</t>
@@ -5579,15 +5528,15 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>2</v>
       </c>
@@ -5636,7 +5585,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
           <t>False</t>
@@ -5672,15 +5620,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>2</v>
       </c>
@@ -5729,7 +5677,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
           <t>False</t>
@@ -5765,15 +5712,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>3</v>
       </c>
@@ -5822,7 +5769,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
           <t>True</t>
@@ -5858,15 +5804,15 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>3</v>
       </c>
@@ -5915,7 +5861,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
           <t>False</t>
@@ -5951,15 +5896,15 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>2</v>
       </c>
@@ -6008,7 +5953,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
           <t>False</t>
@@ -6044,15 +5988,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>3</v>
       </c>
@@ -6101,7 +6045,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
           <t>True</t>
@@ -6137,15 +6080,15 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>4</v>
       </c>
@@ -6194,7 +6137,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>True</t>
@@ -6230,15 +6172,15 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>2</v>
       </c>
@@ -6287,7 +6229,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
           <t>False</t>
@@ -6323,15 +6264,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>3</v>
       </c>
@@ -6380,7 +6321,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
           <t>False</t>
@@ -6416,15 +6356,15 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>2</v>
       </c>
@@ -6473,7 +6413,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>False</t>
@@ -6509,15 +6448,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>2</v>
       </c>
@@ -6566,7 +6505,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
           <t>False</t>
@@ -6602,15 +6540,15 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>4</v>
       </c>
@@ -6700,15 +6638,15 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>3</v>
       </c>
@@ -6758,7 +6696,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
           <t>False</t>
@@ -6794,15 +6731,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>3</v>
       </c>
@@ -6892,15 +6829,15 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>4</v>
       </c>
@@ -6951,7 +6888,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
           <t>True</t>
@@ -6987,15 +6923,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>5</v>
       </c>
@@ -7085,15 +7021,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>4</v>
       </c>
@@ -7184,15 +7120,15 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>3</v>
       </c>
@@ -7282,15 +7218,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>2</v>
       </c>
@@ -7340,7 +7276,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
           <t>False</t>
@@ -7376,15 +7311,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7434,7 +7369,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
           <t>False</t>
@@ -7470,15 +7404,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>5</v>
       </c>
@@ -7568,15 +7502,15 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>2</v>
       </c>
@@ -7625,7 +7559,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
           <t>True</t>
@@ -7661,15 +7594,15 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7718,7 +7651,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
           <t>False</t>
@@ -7757,12 +7689,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>2</v>
       </c>
@@ -7811,7 +7743,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
           <t>False</t>
@@ -7847,15 +7778,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>3</v>
       </c>
@@ -7904,7 +7835,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>False</t>
@@ -7940,15 +7870,15 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>2</v>
       </c>
@@ -7997,7 +7927,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
           <t>False</t>
@@ -8036,12 +7965,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>病態の基礎</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8090,7 +8019,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>False</t>
@@ -8126,15 +8054,15 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>2</v>
       </c>
@@ -8183,7 +8111,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
           <t>False</t>
@@ -8219,15 +8146,15 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>2</v>
       </c>
@@ -8276,7 +8203,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
           <t>False</t>
@@ -8315,12 +8241,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>2</v>
       </c>
@@ -8369,7 +8295,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
           <t>False</t>
@@ -8408,12 +8333,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>2</v>
       </c>
@@ -8462,7 +8387,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
           <t>False</t>
@@ -8498,15 +8422,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>3</v>
       </c>
@@ -8555,7 +8479,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
           <t>False</t>
@@ -8591,15 +8514,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>3</v>
       </c>
@@ -8648,7 +8571,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
           <t>False</t>
@@ -8684,15 +8606,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>2</v>
       </c>
@@ -8741,7 +8663,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
           <t>False</t>
@@ -8777,15 +8698,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>3</v>
       </c>
@@ -8834,7 +8755,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
           <t>False</t>
@@ -8873,12 +8793,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>2</v>
       </c>
@@ -8927,7 +8847,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
           <t>False</t>
@@ -8963,15 +8882,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>2</v>
       </c>
@@ -9021,7 +8940,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
           <t>False</t>
@@ -9057,15 +8975,15 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>3</v>
       </c>
@@ -9114,7 +9032,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
           <t>False</t>
@@ -9150,15 +9067,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>2</v>
       </c>
@@ -9207,7 +9124,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
           <t>False</t>
@@ -9243,15 +9159,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>3</v>
       </c>
@@ -9300,7 +9216,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
           <t>True</t>
@@ -9336,15 +9251,15 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>2</v>
       </c>
@@ -9393,7 +9308,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
           <t>False</t>
@@ -9429,15 +9343,15 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>3</v>
       </c>
@@ -9486,7 +9400,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
           <t>False</t>
@@ -9522,15 +9435,15 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>3</v>
       </c>
@@ -9579,7 +9492,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
           <t>False</t>
@@ -9615,15 +9527,15 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>2</v>
       </c>
@@ -9672,7 +9584,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
           <t>False</t>
@@ -9708,15 +9619,15 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>2</v>
       </c>
@@ -9765,7 +9676,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
           <t>False</t>
@@ -9801,15 +9711,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>3</v>
       </c>
@@ -9858,7 +9768,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
           <t>False</t>
@@ -9894,15 +9803,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>2</v>
       </c>
@@ -9951,7 +9860,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
           <t>False</t>
@@ -9987,15 +9895,15 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>3</v>
       </c>
@@ -10044,7 +9952,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
           <t>False</t>
@@ -10080,15 +9987,15 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>3</v>
       </c>
@@ -10137,7 +10044,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
           <t>False</t>
@@ -10173,15 +10079,15 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10230,7 +10136,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
           <t>False</t>
@@ -10266,15 +10171,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>4</v>
       </c>
@@ -10367,12 +10272,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>1</v>
       </c>
@@ -10421,7 +10326,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
           <t>False</t>
@@ -10460,12 +10364,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>2</v>
       </c>
@@ -10514,7 +10418,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
           <t>False</t>
@@ -10550,15 +10453,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>2</v>
       </c>
@@ -10607,7 +10510,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
           <t>False</t>
@@ -10643,15 +10545,15 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>3</v>
       </c>
@@ -10700,7 +10602,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
           <t>False</t>
@@ -10736,15 +10637,15 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>2</v>
       </c>
@@ -10793,7 +10694,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
           <t>False</t>
@@ -10829,15 +10729,15 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>2</v>
       </c>
@@ -10886,7 +10786,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
           <t>False</t>
@@ -10922,15 +10821,15 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>3</v>
       </c>
@@ -10979,7 +10878,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
           <t>False</t>
@@ -11015,15 +10913,15 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>3</v>
       </c>
@@ -11072,7 +10970,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
           <t>True</t>
@@ -11108,15 +11005,15 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>2</v>
       </c>
@@ -11165,7 +11062,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
           <t>False</t>
@@ -11204,12 +11100,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11258,7 +11154,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
           <t>False</t>
@@ -11294,15 +11189,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>2</v>
       </c>
@@ -11351,7 +11246,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
           <t>False</t>
@@ -11390,12 +11284,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>疾患の診断と治療</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>2</v>
       </c>
@@ -11444,7 +11338,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
           <t>False</t>
@@ -11480,15 +11373,15 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>2</v>
       </c>
@@ -11537,7 +11430,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
           <t>False</t>
@@ -11573,15 +11465,15 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>3</v>
       </c>
@@ -11630,7 +11522,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
           <t>False</t>
@@ -11666,15 +11557,15 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11723,7 +11614,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
           <t>False</t>
@@ -11759,15 +11649,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>3</v>
       </c>
@@ -11816,7 +11706,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
           <t>False</t>
@@ -11852,15 +11741,15 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>1</v>
       </c>
@@ -11909,7 +11798,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
           <t>False</t>
@@ -11945,15 +11833,15 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>2</v>
       </c>
@@ -12002,7 +11890,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
           <t>False</t>
@@ -12038,15 +11925,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>3</v>
       </c>
@@ -12095,7 +11982,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
           <t>False</t>
@@ -12131,15 +12017,15 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>4</v>
       </c>
@@ -12188,7 +12074,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
           <t>True</t>
@@ -12224,15 +12109,15 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>3</v>
       </c>
@@ -12281,7 +12166,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
           <t>True</t>
@@ -12317,15 +12201,15 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>4</v>
       </c>
@@ -12374,7 +12258,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
           <t>True</t>
@@ -12410,15 +12293,15 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>3</v>
       </c>
@@ -12467,7 +12350,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
           <t>False</t>
@@ -12506,12 +12388,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>2</v>
       </c>
@@ -12560,7 +12442,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
           <t>False</t>
@@ -12596,15 +12477,15 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>2</v>
       </c>
@@ -12653,7 +12534,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
           <t>False</t>
@@ -12689,15 +12569,15 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>3</v>
       </c>
@@ -12746,7 +12626,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
           <t>True</t>
@@ -12782,15 +12661,15 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>3</v>
       </c>
@@ -12880,15 +12759,15 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>3</v>
       </c>
@@ -12937,7 +12816,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
           <t>True</t>
@@ -12973,15 +12851,15 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>4</v>
       </c>
@@ -13030,7 +12908,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
           <t>False</t>
@@ -13066,15 +12943,15 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>2</v>
       </c>
@@ -13123,7 +13000,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
           <t>False</t>
@@ -13159,15 +13035,15 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>2</v>
       </c>
@@ -13216,7 +13092,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
           <t>True</t>
@@ -13252,15 +13127,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>4</v>
       </c>
@@ -13350,15 +13225,15 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>3</v>
       </c>
@@ -13407,7 +13282,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
           <t>True</t>
@@ -13443,15 +13317,15 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>3</v>
       </c>
@@ -13500,7 +13374,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
           <t>True</t>
@@ -13536,15 +13409,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>2</v>
       </c>
@@ -13593,7 +13466,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
           <t>False</t>
@@ -13629,15 +13501,15 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>4</v>
       </c>
@@ -13727,15 +13599,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>4</v>
       </c>
@@ -13825,15 +13697,15 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>4</v>
       </c>
@@ -13923,15 +13795,15 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>5</v>
       </c>
@@ -14021,15 +13893,15 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>4</v>
       </c>
@@ -14119,15 +13991,15 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>3</v>
       </c>
@@ -14217,15 +14089,15 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>3</v>
       </c>
@@ -14315,15 +14187,15 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>2</v>
       </c>
@@ -14373,7 +14245,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
           <t>False</t>
@@ -14409,15 +14280,15 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>5</v>
       </c>
@@ -14507,15 +14378,15 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>3</v>
       </c>
@@ -14564,7 +14435,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
           <t>False</t>

--- a/CO国試data/CO_questions_2019.xlsx
+++ b/CO国試data/CO_questions_2019.xlsx
@@ -542,12 +542,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>外眼筋</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>遺伝</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>遺伝</t>
+          <t>遺伝子</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>免疫機構</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>免疫機構</t>
+          <t>免疫系の構成・機能</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -818,12 +818,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>病態の基礎</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>病態の基礎</t>
+          <t>病因と疾病の種類</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -910,12 +910,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>疾患の診断と治療</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>疾患の診断と治療</t>
+          <t>脳、神経系疾患</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>視覚伝導路</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>心身の成長・発達、加齢</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>心身の成長・発達、加齢</t>
+          <t>加齢、老化</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>結膜</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2014,12 +2014,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2572,12 +2572,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2756,12 +2756,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2848,12 +2848,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2940,12 +2940,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼圧検査</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3124,12 +3124,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3216,12 +3216,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3308,12 +3308,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3400,12 +3400,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3492,12 +3492,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3780,12 +3780,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>隅角検査</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3872,12 +3872,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼圧検査</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3964,12 +3964,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>中心フリッカ検査</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼瞼</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4332,12 +4332,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -4516,12 +4516,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -4700,12 +4700,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -4792,12 +4792,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -4884,12 +4884,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -4976,12 +4976,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>小児視能特性</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5160,12 +5160,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5252,12 +5252,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -5344,12 +5344,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -5436,12 +5436,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -5620,12 +5620,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -5712,12 +5712,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -5896,12 +5896,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>眼位と眼球運動</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>両眼視</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -6264,12 +6264,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -6356,12 +6356,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -6540,12 +6540,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -6731,12 +6731,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -6829,12 +6829,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -6923,12 +6923,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -7021,12 +7021,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>硝子体</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -7311,12 +7311,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -7404,12 +7404,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>水晶体</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -7502,12 +7502,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -7594,12 +7594,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -7686,12 +7686,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>健康の指標</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -7778,12 +7778,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -7870,12 +7870,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -7962,12 +7962,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>病態の基礎</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>病態の基礎</t>
+          <t>病因と疾病の種類</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -8054,12 +8054,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -8146,12 +8146,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -8330,12 +8330,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -8422,12 +8422,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -8514,12 +8514,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -8790,12 +8790,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -8882,12 +8882,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -8975,12 +8975,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -9159,12 +9159,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -9251,12 +9251,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -9343,12 +9343,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -9435,12 +9435,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -9527,12 +9527,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -9619,12 +9619,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>中心フリッカ検査</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -9711,12 +9711,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -9803,12 +9803,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -9895,12 +9895,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>前眼部、透光体検査</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -9987,12 +9987,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -10079,12 +10079,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -10361,12 +10361,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -10453,12 +10453,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -10545,12 +10545,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -10637,12 +10637,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -10729,12 +10729,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -10821,12 +10821,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼窩</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -10913,12 +10913,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -11097,12 +11097,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -11189,12 +11189,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -11281,12 +11281,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>疾患の診断と治療</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>疾患の診断と治療</t>
+          <t>脳、神経系疾患</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -11373,12 +11373,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -11465,12 +11465,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>水晶体</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -11557,12 +11557,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -11741,12 +11741,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>硝子体</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -11833,12 +11833,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>涙器</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -11925,12 +11925,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼瞼</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -12017,12 +12017,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -12109,12 +12109,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>基本的知識</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -12201,12 +12201,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>両眼視</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -12293,12 +12293,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -12385,12 +12385,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -12477,12 +12477,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -12569,12 +12569,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -12661,12 +12661,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>両眼視</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -12759,12 +12759,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>基本的知識</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -12851,12 +12851,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -12943,12 +12943,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -13035,12 +13035,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -13127,12 +13127,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -13225,12 +13225,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -13409,12 +13409,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -13501,12 +13501,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -13599,12 +13599,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視野検査</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -13697,12 +13697,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -13795,12 +13795,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -13893,12 +13893,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -13991,12 +13991,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -14089,12 +14089,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -14187,12 +14187,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -14378,12 +14378,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>

--- a/CO国試data/CO_questions_2019.xlsx
+++ b/CO国試data/CO_questions_2019.xlsx
@@ -550,7 +550,6 @@
           <t>外眼筋</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -642,7 +641,11 @@
           <t>遺伝子</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>染色体</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -734,7 +737,6 @@
           <t>免疫系の構成・機能</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -826,7 +828,11 @@
           <t>病因と疾病の種類</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>代謝異常</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -918,7 +924,6 @@
           <t>脳、神経系疾患</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -1010,7 +1015,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1102,7 +1106,11 @@
           <t>視覚伝導路</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>視交叉</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1194,7 +1202,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>3</v>
       </c>
@@ -1286,7 +1293,6 @@
           <t>加齢、老化</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1378,7 +1384,11 @@
           <t>結膜</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>結膜炎</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -1470,7 +1480,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>3</v>
       </c>
@@ -1562,7 +1571,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>3</v>
       </c>
@@ -1654,7 +1662,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -1746,7 +1758,6 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>3</v>
       </c>
@@ -1838,7 +1849,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -1930,7 +1940,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -2022,7 +2031,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -2114,7 +2122,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>3</v>
       </c>
@@ -2206,7 +2213,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -2298,7 +2304,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -2390,7 +2400,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>3</v>
       </c>
@@ -2482,7 +2491,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>4</v>
       </c>
@@ -2580,7 +2593,11 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>眼振の手術</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>3</v>
       </c>
@@ -2672,7 +2689,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>3</v>
       </c>
@@ -2764,7 +2785,11 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>患者の安全管理</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>1</v>
       </c>
@@ -2856,7 +2881,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -2948,7 +2972,6 @@
           <t>眼圧検査</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -3040,7 +3063,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -3132,7 +3154,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>3</v>
       </c>
@@ -3224,7 +3245,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>3</v>
       </c>
@@ -3316,7 +3336,11 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>遠見、近見視力検査</t>
+        </is>
+      </c>
       <c r="H32" t="n">
         <v>3</v>
       </c>
@@ -3408,7 +3432,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>3</v>
       </c>
@@ -3500,7 +3523,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>測定法</t>
+        </is>
+      </c>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -3592,7 +3619,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H35" t="n">
         <v>4</v>
       </c>
@@ -3690,7 +3721,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>3</v>
       </c>
@@ -3788,7 +3818,6 @@
           <t>隅角検査</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>2</v>
       </c>
@@ -3880,7 +3909,6 @@
           <t>眼圧検査</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>1</v>
       </c>
@@ -3972,7 +4000,11 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>倒像、直像鏡検査</t>
+        </is>
+      </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4064,7 +4096,6 @@
           <t>中心フリッカ検査</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>2</v>
       </c>
@@ -4156,7 +4187,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>うっ血乳頭</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -4248,7 +4283,11 @@
           <t>眼瞼</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>眼瞼下垂</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>1</v>
       </c>
@@ -4340,7 +4379,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>3</v>
       </c>
@@ -4432,7 +4475,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>3</v>
       </c>
@@ -4524,7 +4571,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -4616,7 +4662,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>3</v>
       </c>
@@ -4708,7 +4753,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>3</v>
       </c>
@@ -4800,7 +4844,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H48" t="n">
         <v>2</v>
       </c>
@@ -4892,7 +4940,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>3</v>
       </c>
@@ -4984,7 +5031,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H50" t="n">
         <v>3</v>
       </c>
@@ -5076,7 +5127,6 @@
           <t>小児視能特性</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>3</v>
       </c>
@@ -5168,7 +5218,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>3</v>
       </c>
@@ -5260,7 +5309,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>4</v>
       </c>
@@ -5352,7 +5400,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>光の性質、幾何光学</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>2</v>
       </c>
@@ -5444,7 +5496,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>2</v>
       </c>
@@ -5536,7 +5587,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H56" t="n">
         <v>2</v>
       </c>
@@ -5628,7 +5683,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>2</v>
       </c>
@@ -5720,7 +5779,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>3</v>
       </c>
@@ -5812,7 +5870,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>3</v>
       </c>
@@ -5904,7 +5961,6 @@
           <t>眼位と眼球運動</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>2</v>
       </c>
@@ -5996,7 +6052,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>上下斜視</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>3</v>
       </c>
@@ -6088,7 +6148,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>4</v>
       </c>
@@ -6180,7 +6239,11 @@
           <t>両眼視</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>網膜対応、両眼視野</t>
+        </is>
+      </c>
       <c r="H63" t="n">
         <v>2</v>
       </c>
@@ -6272,7 +6335,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>3</v>
       </c>
@@ -6364,7 +6426,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H65" t="n">
         <v>2</v>
       </c>
@@ -6456,7 +6522,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>2</v>
       </c>
@@ -6548,7 +6613,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>視神経症</t>
+        </is>
+      </c>
       <c r="H67" t="n">
         <v>4</v>
       </c>
@@ -6646,7 +6715,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>3</v>
       </c>
@@ -6739,7 +6807,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>視交叉から後頭葉までの視覚伝導路の疾患</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>3</v>
       </c>
@@ -6837,7 +6909,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>4</v>
       </c>
@@ -6931,7 +7002,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>5</v>
       </c>
@@ -7029,7 +7099,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H72" t="n">
         <v>4</v>
       </c>
@@ -7128,7 +7202,11 @@
           <t>硝子体</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>硝子体出血、混濁、後部硝子体剥離</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>3</v>
       </c>
@@ -7226,7 +7304,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>2</v>
       </c>
@@ -7319,7 +7396,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>4</v>
       </c>
@@ -7412,7 +7493,11 @@
           <t>水晶体</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>白内障</t>
+        </is>
+      </c>
       <c r="H76" t="n">
         <v>5</v>
       </c>
@@ -7510,7 +7595,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H77" t="n">
         <v>2</v>
       </c>
@@ -7602,7 +7691,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7694,7 +7782,11 @@
           <t>健康の指標</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>人口問題</t>
+        </is>
+      </c>
       <c r="H79" t="n">
         <v>2</v>
       </c>
@@ -7786,7 +7878,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>視神経炎</t>
+        </is>
+      </c>
       <c r="H80" t="n">
         <v>3</v>
       </c>
@@ -7878,7 +7974,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>2</v>
       </c>
@@ -7970,7 +8065,11 @@
           <t>病因と疾病の種類</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>退行性病変</t>
+        </is>
+      </c>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8062,7 +8161,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>うっ血乳頭</t>
+        </is>
+      </c>
       <c r="H83" t="n">
         <v>2</v>
       </c>
@@ -8154,7 +8257,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>2</v>
       </c>
@@ -8246,7 +8348,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>2</v>
       </c>
@@ -8338,7 +8439,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>2</v>
       </c>
@@ -8430,7 +8530,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>乱視</t>
+        </is>
+      </c>
       <c r="H87" t="n">
         <v>3</v>
       </c>
@@ -8522,7 +8626,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>3</v>
       </c>
@@ -8614,7 +8717,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H89" t="n">
         <v>2</v>
       </c>
@@ -8706,7 +8813,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H90" t="n">
         <v>3</v>
       </c>
@@ -8798,7 +8909,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>2</v>
       </c>
@@ -8890,7 +9000,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>2</v>
       </c>
@@ -8983,7 +9092,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>3</v>
       </c>
@@ -9075,7 +9188,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H94" t="n">
         <v>2</v>
       </c>
@@ -9167,7 +9284,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>3</v>
       </c>
@@ -9259,7 +9375,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H96" t="n">
         <v>2</v>
       </c>
@@ -9351,7 +9471,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H97" t="n">
         <v>3</v>
       </c>
@@ -9443,7 +9567,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>3</v>
       </c>
@@ -9535,7 +9658,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>2</v>
       </c>
@@ -9627,7 +9749,11 @@
           <t>中心フリッカ検査</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>限界フリッカ値〈CFF〉</t>
+        </is>
+      </c>
       <c r="H100" t="n">
         <v>2</v>
       </c>
@@ -9719,7 +9845,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>3</v>
       </c>
@@ -9811,7 +9936,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>2</v>
       </c>
@@ -9903,7 +10027,11 @@
           <t>前眼部、透光体検査</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>細隙灯顕微鏡検査</t>
+        </is>
+      </c>
       <c r="H103" t="n">
         <v>3</v>
       </c>
@@ -9995,7 +10123,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>3</v>
       </c>
@@ -10087,7 +10214,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>瞳孔緊張症〈緊張性瞳孔〉</t>
+        </is>
+      </c>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10179,7 +10310,11 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>倒像、直像鏡検査</t>
+        </is>
+      </c>
       <c r="H106" t="n">
         <v>4</v>
       </c>
@@ -10277,7 +10412,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>1</v>
       </c>
@@ -10369,7 +10503,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>2</v>
       </c>
@@ -10461,7 +10594,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>2</v>
       </c>
@@ -10553,7 +10685,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>3</v>
       </c>
@@ -10645,7 +10776,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H111" t="n">
         <v>2</v>
       </c>
@@ -10737,7 +10872,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>2</v>
       </c>
@@ -10829,7 +10963,11 @@
           <t>眼窩</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>眼球突出、陥凹</t>
+        </is>
+      </c>
       <c r="H113" t="n">
         <v>3</v>
       </c>
@@ -10921,7 +11059,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>瞳孔緊張症〈緊張性瞳孔〉</t>
+        </is>
+      </c>
       <c r="H114" t="n">
         <v>3</v>
       </c>
@@ -11013,7 +11155,11 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>涙液層破壊時間〈BUT〉</t>
+        </is>
+      </c>
       <c r="H115" t="n">
         <v>2</v>
       </c>
@@ -11105,7 +11251,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11197,7 +11342,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H117" t="n">
         <v>2</v>
       </c>
@@ -11289,7 +11438,6 @@
           <t>脳、神経系疾患</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>2</v>
       </c>
@@ -11381,7 +11529,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>2</v>
       </c>
@@ -11473,7 +11620,11 @@
           <t>水晶体</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>白内障</t>
+        </is>
+      </c>
       <c r="H120" t="n">
         <v>3</v>
       </c>
@@ -11565,7 +11716,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11657,7 +11807,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H122" t="n">
         <v>3</v>
       </c>
@@ -11749,7 +11903,11 @@
           <t>硝子体</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>硝子体出血、混濁、後部硝子体剥離</t>
+        </is>
+      </c>
       <c r="H123" t="n">
         <v>1</v>
       </c>
@@ -11841,7 +11999,11 @@
           <t>涙器</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>鼻涙管閉塞</t>
+        </is>
+      </c>
       <c r="H124" t="n">
         <v>2</v>
       </c>
@@ -11933,7 +12095,11 @@
           <t>眼瞼</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>眼瞼下垂</t>
+        </is>
+      </c>
       <c r="H125" t="n">
         <v>3</v>
       </c>
@@ -12025,7 +12191,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H126" t="n">
         <v>4</v>
       </c>
@@ -12117,7 +12287,11 @@
           <t>基本的知識</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
       <c r="H127" t="n">
         <v>3</v>
       </c>
@@ -12209,7 +12383,11 @@
           <t>両眼視</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>成立の生理学的機序</t>
+        </is>
+      </c>
       <c r="H128" t="n">
         <v>4</v>
       </c>
@@ -12301,7 +12479,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>3</v>
       </c>
@@ -12393,7 +12570,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>2</v>
       </c>
@@ -12485,7 +12661,6 @@
           <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>2</v>
       </c>
@@ -12577,7 +12752,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H132" t="n">
         <v>3</v>
       </c>
@@ -12669,7 +12848,11 @@
           <t>両眼視</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Panumの融像感覚圏</t>
+        </is>
+      </c>
       <c r="H133" t="n">
         <v>3</v>
       </c>
@@ -12767,7 +12950,11 @@
           <t>基本的知識</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
       <c r="H134" t="n">
         <v>3</v>
       </c>
@@ -12859,7 +13046,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>4</v>
       </c>
@@ -12951,7 +13137,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>不同視弱視</t>
+        </is>
+      </c>
       <c r="H136" t="n">
         <v>2</v>
       </c>
@@ -13043,7 +13233,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>斜視弱視</t>
+        </is>
+      </c>
       <c r="H137" t="n">
         <v>2</v>
       </c>
@@ -13135,7 +13329,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>4</v>
       </c>
@@ -13233,7 +13426,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H139" t="n">
         <v>3</v>
       </c>
@@ -13325,7 +13522,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>3</v>
       </c>
@@ -13417,7 +13613,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H141" t="n">
         <v>2</v>
       </c>
@@ -13509,7 +13709,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>4</v>
       </c>
@@ -13607,7 +13806,11 @@
           <t>視野検査</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>動的、静的視野測定法（自動視野計を含む）</t>
+        </is>
+      </c>
       <c r="H143" t="n">
         <v>4</v>
       </c>
@@ -13705,7 +13908,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>4</v>
       </c>
@@ -13803,7 +14005,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>5</v>
       </c>
@@ -13901,7 +14102,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H146" t="n">
         <v>4</v>
       </c>
@@ -13999,7 +14204,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>うっ血乳頭</t>
+        </is>
+      </c>
       <c r="H147" t="n">
         <v>3</v>
       </c>
@@ -14097,7 +14306,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>3</v>
       </c>
@@ -14195,7 +14403,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>2</v>
       </c>
@@ -14288,7 +14495,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>5</v>
       </c>
@@ -14386,7 +14592,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H151" t="n">
         <v>3</v>
       </c>

--- a/CO国試data/CO_questions_2019.xlsx
+++ b/CO国試data/CO_questions_2019.xlsx
@@ -598,10 +598,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S2" t="b">
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -694,10 +692,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S3" t="b">
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -785,10 +781,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S4" t="b">
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,10 +966,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S6" t="b">
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1063,10 +1055,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S7" t="b">
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1159,10 +1149,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S8" t="b">
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1250,10 +1238,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S9" t="b">
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1341,10 +1327,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S10" t="b">
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1528,10 +1512,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S12" t="b">
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1619,10 +1601,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S13" t="b">
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1715,10 +1695,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S14" t="b">
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1897,10 +1875,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S16" t="b">
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1988,10 +1964,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S17" t="b">
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2079,10 +2053,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S18" t="b">
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2170,10 +2142,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S19" t="b">
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2261,10 +2231,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S20" t="b">
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2357,10 +2325,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S21" t="b">
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2448,10 +2414,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S22" t="b">
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2550,10 +2514,8 @@
           <t>2019_co_19_am022.jpg</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S23" t="b">
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2646,10 +2608,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S24" t="b">
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2838,10 +2798,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S26" t="b">
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2929,10 +2887,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S27" t="b">
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3020,10 +2976,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S28" t="b">
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3111,10 +3065,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S29" t="b">
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3202,10 +3154,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S30" t="b">
+        <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3293,10 +3243,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S31" t="b">
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3389,10 +3337,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S32" t="b">
+        <v>0</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3576,10 +3522,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S34" t="b">
+        <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3678,10 +3622,8 @@
           <t>2019_co_19_am034.jpg</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S35" t="b">
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3775,10 +3717,8 @@
           <t>2019_co_19_am035.jpg</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S36" t="b">
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3866,10 +3806,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S37" t="b">
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3957,10 +3895,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S38" t="b">
+        <v>0</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4053,10 +3989,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S39" t="b">
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4144,10 +4078,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S40" t="b">
+        <v>0</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4240,10 +4172,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S41" t="b">
+        <v>0</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4336,10 +4266,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S42" t="b">
+        <v>0</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4619,10 +4547,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S45" t="b">
+        <v>0</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4710,10 +4636,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S46" t="b">
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4801,10 +4725,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S47" t="b">
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4897,10 +4819,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S48" t="b">
+        <v>0</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4988,10 +4908,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S49" t="b">
+        <v>0</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5175,10 +5093,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S51" t="b">
+        <v>0</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5266,10 +5182,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S52" t="b">
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5357,10 +5271,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S53" t="b">
+        <v>0</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5544,10 +5456,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S55" t="b">
+        <v>0</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5640,10 +5550,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S56" t="b">
+        <v>0</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5736,10 +5644,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S57" t="b">
+        <v>0</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5918,10 +5824,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S59" t="b">
+        <v>0</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6009,10 +5913,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S60" t="b">
+        <v>0</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6292,10 +6194,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S63" t="b">
+        <v>0</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6383,10 +6283,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S64" t="b">
+        <v>0</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6479,10 +6377,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S65" t="b">
+        <v>0</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6570,10 +6466,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S66" t="b">
+        <v>0</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6672,10 +6566,8 @@
           <t>2019_co_19_am066.jpg</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S67" t="b">
+        <v>0</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6764,10 +6656,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S68" t="b">
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6866,10 +6756,8 @@
           <t>2019_co_19_am068.jpg</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S69" t="b">
+        <v>0</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6959,10 +6847,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S70" t="b">
+        <v>0</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7159,10 +7045,8 @@
           <t>2019_co_19_am071.jpg</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S72" t="b">
+        <v>0</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7261,10 +7145,8 @@
           <t>2019_co_19_am072.jpg</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S73" t="b">
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7353,10 +7235,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S74" t="b">
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7450,10 +7330,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S75" t="b">
+        <v>0</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7552,10 +7430,8 @@
           <t>2019_co_19_am075.jpg</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S76" t="b">
+        <v>0</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7648,10 +7524,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S77" t="b">
+        <v>0</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7739,10 +7613,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S78" t="b">
+        <v>0</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -7835,10 +7707,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S79" t="b">
+        <v>0</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -7931,10 +7801,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S80" t="b">
+        <v>0</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8022,10 +7890,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S81" t="b">
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8118,10 +7984,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S82" t="b">
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8214,10 +8078,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S83" t="b">
+        <v>0</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8305,10 +8167,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S84" t="b">
+        <v>0</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8396,10 +8256,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S85" t="b">
+        <v>0</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8487,10 +8345,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S86" t="b">
+        <v>0</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8583,10 +8439,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S87" t="b">
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8674,10 +8528,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S88" t="b">
+        <v>0</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -8770,10 +8622,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S89" t="b">
+        <v>0</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -8866,10 +8716,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S90" t="b">
+        <v>0</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -8957,10 +8805,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S91" t="b">
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9049,10 +8895,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S92" t="b">
+        <v>0</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9145,10 +8989,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S93" t="b">
+        <v>0</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9241,10 +9083,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S94" t="b">
+        <v>0</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9428,10 +9268,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S96" t="b">
+        <v>0</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9524,10 +9362,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S97" t="b">
+        <v>0</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -9615,10 +9451,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S98" t="b">
+        <v>0</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -9706,10 +9540,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S99" t="b">
+        <v>0</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -9802,10 +9634,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S100" t="b">
+        <v>0</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -9893,10 +9723,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S101" t="b">
+        <v>0</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -9984,10 +9812,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S102" t="b">
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10080,10 +9906,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S103" t="b">
+        <v>0</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10171,10 +9995,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S104" t="b">
+        <v>0</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10267,10 +10089,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S105" t="b">
+        <v>0</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10369,10 +10189,8 @@
           <t>2019_co_19_pm030.jpg</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S106" t="b">
+        <v>0</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10460,10 +10278,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S107" t="b">
+        <v>0</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -10551,10 +10367,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S108" t="b">
+        <v>0</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -10642,10 +10456,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S109" t="b">
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -10733,10 +10545,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S110" t="b">
+        <v>0</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10829,10 +10639,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S111" t="b">
+        <v>0</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -10920,10 +10728,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S112" t="b">
+        <v>0</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11016,10 +10822,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S113" t="b">
+        <v>0</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11112,10 +10916,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S114" t="b">
+        <v>0</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11208,10 +11010,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S115" t="b">
+        <v>0</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11299,10 +11099,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S116" t="b">
+        <v>0</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11395,10 +11193,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S117" t="b">
+        <v>0</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11486,10 +11282,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S118" t="b">
+        <v>0</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -11577,10 +11371,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S119" t="b">
+        <v>0</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -11673,10 +11465,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S120" t="b">
+        <v>0</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -11764,10 +11554,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S121" t="b">
+        <v>0</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -11860,10 +11648,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S122" t="b">
+        <v>0</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -11956,10 +11742,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S123" t="b">
+        <v>0</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12052,10 +11836,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S124" t="b">
+        <v>0</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12148,10 +11930,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S125" t="b">
+        <v>0</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12340,10 +12120,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S127" t="b">
+        <v>0</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -12527,10 +12305,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S129" t="b">
+        <v>0</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -12618,10 +12394,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S130" t="b">
+        <v>0</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -12709,10 +12483,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S131" t="b">
+        <v>0</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -12805,10 +12577,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S132" t="b">
+        <v>0</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -12907,10 +12677,8 @@
           <t>2019_co_19_pm057.jpg</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S133" t="b">
+        <v>0</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13003,10 +12771,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S134" t="b">
+        <v>0</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13094,10 +12860,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S135" t="b">
+        <v>0</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13190,10 +12954,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S136" t="b">
+        <v>0</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13383,10 +13145,8 @@
           <t>2019_co_19_pm062.jpg</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S138" t="b">
+        <v>0</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -13479,10 +13239,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S139" t="b">
+        <v>0</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -13570,10 +13328,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S140" t="b">
+        <v>0</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -13666,10 +13422,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S141" t="b">
+        <v>0</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -13763,10 +13517,8 @@
           <t>2019_co_19_pm066.jpg</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S142" t="b">
+        <v>0</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -13865,10 +13617,8 @@
           <t>2019_co_19_pm067.jpg</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S143" t="b">
+        <v>0</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14263,10 +14013,8 @@
           <t>2019_co_19_pm071.jpg</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S147" t="b">
+        <v>0</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -14452,10 +14200,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S149" t="b">
+        <v>0</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -14549,10 +14295,8 @@
           <t>2019_co_19_pm074.jpg</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S150" t="b">
+        <v>0</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -14645,10 +14389,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S151" t="b">
+        <v>0</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>

--- a/CO国試data/CO_questions_2019.xlsx
+++ b/CO国試data/CO_questions_2019.xlsx
@@ -862,7 +862,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -875,10 +875,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S5" t="b">
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1408,7 +1406,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1421,10 +1419,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S11" t="b">
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,7 +1767,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1784,10 +1780,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S15" t="b">
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2689,7 +2683,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2702,10 +2696,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S25" t="b">
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3413,7 +3405,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3426,10 +3418,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S33" t="b">
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4347,7 +4337,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4360,10 +4350,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S43" t="b">
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4443,7 +4431,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4456,10 +4444,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S44" t="b">
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4989,7 +4975,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5002,10 +4988,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S50" t="b">
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5352,7 +5336,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5365,10 +5349,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S54" t="b">
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5720,7 +5702,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -5733,10 +5715,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S58" t="b">
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5994,7 +5974,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6007,10 +5987,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S61" t="b">
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6085,7 +6063,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6098,10 +6076,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S62" t="b">
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6924,7 +6900,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -6942,10 +6918,8 @@
           <t>2019_co_19_am070.jpg</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S71" t="b">
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9159,7 +9133,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -9172,10 +9146,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S95" t="b">
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -12011,7 +11983,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -12024,10 +11996,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S126" t="b">
+        <v>1</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -12201,7 +12171,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -12214,10 +12184,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S128" t="b">
+        <v>1</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13035,7 +13003,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -13048,10 +13016,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S137" t="b">
+        <v>1</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -13315,7 +13281,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>ABCDE</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -13329,7 +13295,7 @@
         </is>
       </c>
       <c r="S140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -13694,7 +13660,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -13712,10 +13678,8 @@
           <t>2019_co_19_pm068.jpg</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S144" t="b">
+        <v>1</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -13791,7 +13755,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -13809,10 +13773,8 @@
           <t>2019_co_19_pm069.jpg</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S145" t="b">
+        <v>1</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -13893,7 +13855,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -13911,10 +13873,8 @@
           <t>2019_co_19_pm070.jpg</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S146" t="b">
+        <v>1</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -14090,7 +14050,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -14108,10 +14068,8 @@
           <t>2019_co_19_pm072.jpg</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S148" t="b">
+        <v>1</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
